--- a/data/raw/인천 25년/항공통계상세조회(노선) (3).xlsx
+++ b/data/raw/인천 25년/항공통계상세조회(노선) (3).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="571">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>35399</t>
-  </si>
-  <si>
-    <t>5992413</t>
-  </si>
-  <si>
-    <t>349320</t>
+    <t>17696</t>
+  </si>
+  <si>
+    <t>2855102</t>
+  </si>
+  <si>
+    <t>168456</t>
   </si>
   <si>
     <t>인천(ICN)</t>
@@ -65,1801 +65,1642 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>395930</t>
-  </si>
-  <si>
-    <t>9972</t>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>198387</t>
+  </si>
+  <si>
+    <t>4938</t>
   </si>
   <si>
     <t>고마스(KMQ)</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>1840</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>과달라하라(GDL)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>괌(GUM)</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>23455</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>광저우(CAN)</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>31003</t>
+  </si>
+  <si>
+    <t>2532</t>
+  </si>
+  <si>
+    <t>구마모도(KMJ)</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>11696</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>16537</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>나가사키(NGS)</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2641</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>49035</t>
+  </si>
+  <si>
+    <t>1716</t>
+  </si>
+  <si>
+    <t>나트랑캄란(CXR)</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>72800</t>
+  </si>
+  <si>
+    <t>662</t>
+  </si>
+  <si>
+    <t>난징(NKG)</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>12155</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>난퉁(NTG)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>누르술탄 나자르바예프(NQZ)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1243</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>뉴왁(EWR)</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>5127</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>뉴욕 JFK(JFK)</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>29475</t>
+  </si>
+  <si>
+    <t>3955</t>
+  </si>
+  <si>
+    <t>니이가타(KIJ)</t>
+  </si>
+  <si>
+    <t>1675</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>다가마스(TAK)</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>10534</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>다낭(DAD)</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>89278</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>9844</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>다카(DAC)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>달라스(DFW)</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>15628</t>
+  </si>
+  <si>
+    <t>3018</t>
+  </si>
+  <si>
+    <t>달랏(DLI)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>2569</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>대구(TAE)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>대련(DLC)</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>16041</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>덴파사(DPS)</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>17218</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>델리(DEL)</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>5289</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>도쿄 나리타(NRT)</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>215487</t>
+  </si>
+  <si>
+    <t>10026</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>15990</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>도쿠시마(TKS)</t>
+  </si>
+  <si>
+    <t>1897</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>도하(DOH)</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>9596</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>돈무앙(DMK)</t>
+  </si>
+  <si>
+    <t>6001</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>두바이(DXB)</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>15218</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>디트로이트(DTW)</t>
+  </si>
+  <si>
+    <t>8342</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>따이쭝(RMQ)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>13281</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>라스베가스(LAS)</t>
+  </si>
+  <si>
+    <t>7830</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>라이프치히(LEJ)</t>
+  </si>
+  <si>
+    <t>랑군(RGN)</t>
+  </si>
+  <si>
+    <t>1852</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>런던히드로(LHR)</t>
+  </si>
+  <si>
+    <t>11544</t>
+  </si>
+  <si>
+    <t>1436</t>
+  </si>
+  <si>
+    <t>로마 파우미치노(FCO)</t>
+  </si>
+  <si>
+    <t>12940</t>
+  </si>
+  <si>
+    <t>567</t>
+  </si>
+  <si>
+    <t>로스앤젤레스(LAX)</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>46866</t>
+  </si>
+  <si>
+    <t>10484</t>
+  </si>
+  <si>
+    <t>루이즈빌(SDF)</t>
+  </si>
+  <si>
+    <t>룩셈부르크(LUX)</t>
+  </si>
+  <si>
+    <t>989</t>
+  </si>
+  <si>
+    <t>리스본(LIS)</t>
+  </si>
+  <si>
+    <t>3027</t>
+  </si>
+  <si>
+    <t>마나스(FRU)</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>749</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>마닐라(MNL)</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>67123</t>
+  </si>
+  <si>
+    <t>3057</t>
+  </si>
+  <si>
+    <t>마드리드(MAD)</t>
+  </si>
+  <si>
+    <t>3890</t>
+  </si>
+  <si>
+    <t>706</t>
+  </si>
+  <si>
+    <t>마이애미(MIA)</t>
+  </si>
+  <si>
+    <t>896</t>
+  </si>
+  <si>
+    <t>마즈야마(MYJ)</t>
+  </si>
+  <si>
+    <t>10650</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>마카오(MFM)</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>16298</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>멕시코(MEX)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>4911</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>멜버른 툴라마린(MEL)</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>멤피스(MEM)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>무단지앙(MDG)</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>뮌헨(MUC)</t>
+  </si>
+  <si>
     <t>28</t>
   </si>
   <si>
-    <t>3849</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>과달라하라(GDL)</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>852</t>
-  </si>
-  <si>
-    <t>괌(GUM)</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>47809</t>
+    <t>6520</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>미네아폴리스(MSP)</t>
+  </si>
+  <si>
+    <t>8595</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>미와사키(KMI)</t>
+  </si>
+  <si>
+    <t>3643</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>밀라노(MXP)</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>4471</t>
+  </si>
+  <si>
+    <t>1458</t>
+  </si>
+  <si>
+    <t>바르샤바(WAW)</t>
+  </si>
+  <si>
+    <t>3776</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>바르셀로나(BCN)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>9471</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>바탐(BTH)</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>반다르세리베가완(BWN)</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>방콕(BKK)</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>92724</t>
+  </si>
+  <si>
+    <t>4683</t>
+  </si>
+  <si>
+    <t>뱅쿠버(YVR)</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>22273</t>
+  </si>
+  <si>
+    <t>1435</t>
+  </si>
+  <si>
+    <t>보스톤(BOS)</t>
+  </si>
+  <si>
+    <t>7714</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>부다페스트(BUD)</t>
+  </si>
+  <si>
+    <t>4282</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>33294</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>브라코프스(VCP)</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>브로츠와프(WRO)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>596</t>
+  </si>
+  <si>
+    <t>브뤼셀(BRU)</t>
+  </si>
+  <si>
+    <t>브리스번(BNE)</t>
+  </si>
+  <si>
+    <t>6813</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>비엔나(VIE)</t>
+  </si>
+  <si>
+    <t>3504</t>
+  </si>
+  <si>
+    <t>2668</t>
+  </si>
+  <si>
+    <t>비엔티안(VTE)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>14962</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>사가(HSG)</t>
+  </si>
+  <si>
+    <t>2810</t>
+  </si>
+  <si>
+    <t>사르고사(ZAZ)</t>
+  </si>
+  <si>
+    <t>사이판(SPN)</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>10192</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>산야(SYX)</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>삿보로(치토세)(CTS)</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>44481</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>샌프란시스코(SFO)</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>32624</t>
+  </si>
+  <si>
+    <t>3204</t>
+  </si>
+  <si>
+    <t>샤먼(XMN)</t>
+  </si>
+  <si>
+    <t>8718</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>샤자르(SHJ)</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>세부(CEB)</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>28090</t>
+  </si>
+  <si>
+    <t>734</t>
+  </si>
+  <si>
+    <t>센다이(SDJ)</t>
+  </si>
+  <si>
+    <t>3404</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>센젠(SZX)</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>21519</t>
+  </si>
+  <si>
+    <t>1320</t>
+  </si>
+  <si>
+    <t>쉬지아쭈앙(석가장)(SJW)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1360</t>
+  </si>
+  <si>
+    <t>스텐스테드(STN)</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>시드니(SYD)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>27555</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>시모지시마(SHI)</t>
+  </si>
+  <si>
+    <t>2542</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>시안(XIY)</t>
+  </si>
+  <si>
+    <t>7228</t>
+  </si>
+  <si>
+    <t>580</t>
+  </si>
+  <si>
+    <t>시애틀(SEA)</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>23248</t>
+  </si>
+  <si>
+    <t>1336</t>
+  </si>
+  <si>
+    <t>시즈오카(FSZ)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>8240</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>시카고 록퍼드(RFD)</t>
+  </si>
+  <si>
+    <t>시카고(ORD)</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>7615</t>
+  </si>
+  <si>
+    <t>8854</t>
+  </si>
+  <si>
+    <t>신시내티(CVG)</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>심양(SHE)</t>
+  </si>
+  <si>
+    <t>15592</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>싱가폴(SIN)</t>
+  </si>
+  <si>
+    <t>388</t>
+  </si>
+  <si>
+    <t>72878</t>
+  </si>
+  <si>
+    <t>5835</t>
+  </si>
+  <si>
+    <t>씨엠립 앙코르(SAI)</t>
+  </si>
+  <si>
+    <t>아디스아바바(ADD)</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>아사이까와(AKJ)</t>
+  </si>
+  <si>
+    <t>1448</t>
+  </si>
+  <si>
+    <t>아쉬가바트(ASB)</t>
+  </si>
+  <si>
+    <t>아오모리(AOJ)</t>
+  </si>
+  <si>
+    <t>1577</t>
+  </si>
+  <si>
+    <t>아틀란타(ATL)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>26773</t>
+  </si>
+  <si>
+    <t>2871</t>
+  </si>
+  <si>
+    <t>알마아타(ALA)</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>5409</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>암스텔담(AMS)</t>
+  </si>
+  <si>
+    <t>10114</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>앵커리지(ANC)</t>
+  </si>
+  <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>양저우타이저우(YTY)</t>
+  </si>
+  <si>
+    <t>1249</t>
+  </si>
+  <si>
+    <t>어저우화후(EHU)</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>연길(YNJ)</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>17608</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>연대(YNT)</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>11186</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>염성(YNZ)</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>오까야마(OKJ)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2420</t>
+  </si>
+  <si>
+    <t>오끼나와(OKA)</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>37187</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>오슬로(OSL)</t>
+  </si>
+  <si>
+    <t>오이다(OIT)</t>
+  </si>
+  <si>
+    <t>4651</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>오크랜드(미)(OAK)</t>
+  </si>
+  <si>
+    <t>오클랜드(AKL)</t>
+  </si>
+  <si>
+    <t>7884</t>
+  </si>
+  <si>
+    <t>563</t>
+  </si>
+  <si>
+    <t>요나고(YGJ)</t>
+  </si>
+  <si>
+    <t>2430</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>우시샤우팡(WUX)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>5627</t>
+  </si>
+  <si>
+    <t>우한(무한)(WUH)</t>
+  </si>
+  <si>
+    <t>3386</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>우후(WHA)</t>
+  </si>
+  <si>
+    <t>울란바토르(신)(UBN)</t>
+  </si>
+  <si>
+    <t>16735</t>
   </si>
   <si>
     <t>831</t>
   </si>
   <si>
-    <t>광저우(CAN)</t>
-  </si>
-  <si>
-    <t>455</t>
-  </si>
-  <si>
-    <t>63206</t>
-  </si>
-  <si>
-    <t>10795</t>
-  </si>
-  <si>
-    <t>구마모도(KMJ)</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>23605</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
+    <t>워싱턴 덜레스(IAD)</t>
+  </si>
+  <si>
+    <t>7780</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>원저우(WNZ)</t>
+  </si>
+  <si>
+    <t>1317</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>웨이하이(WEH)</t>
+  </si>
+  <si>
+    <t>8716</t>
+  </si>
+  <si>
+    <t>이스탄불(IST)</t>
+  </si>
+  <si>
+    <t>19062</t>
+  </si>
+  <si>
+    <t>2286</t>
+  </si>
+  <si>
+    <t>이스트미들랜드(EMA)</t>
+  </si>
+  <si>
+    <t>인디아나폴리스(IND)</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>자무쓰(JMU)</t>
+  </si>
+  <si>
+    <t>자이드(AUH)</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>6889</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>자카르타(CGK)</t>
+  </si>
+  <si>
+    <t>13304</t>
+  </si>
+  <si>
+    <t>1279</t>
+  </si>
+  <si>
+    <t>장가계(대용)(DYG)</t>
+  </si>
+  <si>
+    <t>4441</t>
+  </si>
+  <si>
+    <t>장춘(CGQ)</t>
+  </si>
+  <si>
+    <t>5552</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>정저우(CGO)</t>
+  </si>
+  <si>
+    <t>4394</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>지난(TNA)</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>7212</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>창사(CSX)</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>7040</t>
+  </si>
+  <si>
+    <t>천진(TSN)</t>
+  </si>
+  <si>
+    <t>10025</t>
+  </si>
+  <si>
+    <t>1437</t>
+  </si>
+  <si>
+    <t>청도(TAO)</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>53557</t>
+  </si>
+  <si>
+    <t>952</t>
+  </si>
+  <si>
+    <t>청두(CTU)</t>
+  </si>
+  <si>
+    <t>총킹(중경)(CKG)</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>취리히(ZRH)</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>치앙마이(CNX)</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>20849</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>카고시마(KOJ)</t>
+  </si>
+  <si>
+    <t>6555</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>16097</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>카이로(CAI)</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>카투만두(KTM)</t>
+  </si>
+  <si>
+    <t>2256</t>
+  </si>
+  <si>
+    <t>칼리보(KLO)</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>5949</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>코타키나발루(BKI)</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>19380</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>콜롬보(CMB)</t>
+  </si>
+  <si>
+    <t>1473</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>쿠알라룸푸르(KUL)</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>20508</t>
+  </si>
+  <si>
+    <t>1842</t>
+  </si>
+  <si>
+    <t>쿤밍(KMG)</t>
+  </si>
+  <si>
+    <t>3436</t>
+  </si>
+  <si>
+    <t>퀼른(CGN)</t>
+  </si>
+  <si>
+    <t>클라크 필드(CRK)</t>
+  </si>
+  <si>
+    <t>13321</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>키타큐슈(KKJ)</t>
+  </si>
+  <si>
+    <t>5296</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>타쉬켄트(TAS)</t>
+  </si>
+  <si>
+    <t>9496</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>타이페이(TPE)</t>
+  </si>
+  <si>
+    <t>102620</t>
+  </si>
+  <si>
+    <t>3773</t>
+  </si>
+  <si>
+    <t>타크빌라란(TAG)</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>20196</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>텐푸(TFU)</t>
+  </si>
+  <si>
+    <t>4792</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>토론토(YYZ)</t>
+  </si>
+  <si>
+    <t>15115</t>
+  </si>
+  <si>
+    <t>1894</t>
+  </si>
+  <si>
+    <t>파리 샤를드골(CDG)</t>
+  </si>
+  <si>
+    <t>23437</t>
+  </si>
+  <si>
+    <t>1560</t>
+  </si>
+  <si>
+    <t>페낭(PEN)</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>푸동(PVG)</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>79639</t>
+  </si>
+  <si>
+    <t>7903</t>
+  </si>
+  <si>
+    <t>푸조우(FOC)</t>
+  </si>
+  <si>
+    <t>3926</t>
+  </si>
+  <si>
+    <t>푸켓(HKT)</t>
+  </si>
+  <si>
+    <t>9343</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>푸쿡(PQC)</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>38202</t>
   </si>
   <si>
     <t>363</t>
   </si>
   <si>
-    <t>32578</t>
-  </si>
-  <si>
-    <t>664</t>
-  </si>
-  <si>
-    <t>나가사키(NGS)</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>5223</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>517</t>
-  </si>
-  <si>
-    <t>98281</t>
-  </si>
-  <si>
-    <t>2854</t>
-  </si>
-  <si>
-    <t>나트랑캄란(CXR)</t>
-  </si>
-  <si>
-    <t>872</t>
-  </si>
-  <si>
-    <t>152268</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>난징(NKG)</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>25704</t>
-  </si>
-  <si>
-    <t>428</t>
-  </si>
-  <si>
-    <t>난퉁(NTG)</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>누르술탄 나자르바예프(NQZ)</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2769</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>뉴왁(EWR)</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>10538</t>
-  </si>
-  <si>
-    <t>450</t>
-  </si>
-  <si>
-    <t>뉴욕 JFK(JFK)</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>58175</t>
-  </si>
-  <si>
-    <t>5705</t>
-  </si>
-  <si>
-    <t>니이가타(KIJ)</t>
-  </si>
-  <si>
-    <t>3527</t>
-  </si>
-  <si>
-    <t>다가마스(TAK)</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>21285</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>다낭(DAD)</t>
-  </si>
-  <si>
-    <t>893</t>
-  </si>
-  <si>
-    <t>186094</t>
-  </si>
-  <si>
-    <t>3370</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>20527</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>다카(DAC)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>달라스(DFW)</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>30923</t>
-  </si>
-  <si>
-    <t>3876</t>
-  </si>
-  <si>
-    <t>달랏(DLI)</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>5704</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>대구(TAE)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>3711</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>대련(DLC)</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>33230</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>덴파사(DPS)</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>39189</t>
-  </si>
-  <si>
-    <t>952</t>
-  </si>
-  <si>
-    <t>델리(DEL)</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>13586</t>
-  </si>
-  <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>도쿄 나리타(NRT)</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>432323</t>
-  </si>
-  <si>
-    <t>20039</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>31941</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>도쿠시마(TKS)</t>
-  </si>
-  <si>
-    <t>3930</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>도하(DOH)</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>20374</t>
-  </si>
-  <si>
-    <t>4374</t>
-  </si>
-  <si>
-    <t>돈무앙(DMK)</t>
-  </si>
-  <si>
-    <t>14865</t>
-  </si>
-  <si>
-    <t>701</t>
-  </si>
-  <si>
-    <t>두바이(DXB)</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>33550</t>
-  </si>
-  <si>
-    <t>1946</t>
-  </si>
-  <si>
-    <t>디트로이트(DTW)</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>15611</t>
-  </si>
-  <si>
-    <t>789</t>
-  </si>
-  <si>
-    <t>따이쭝(RMQ)</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>27020</t>
-  </si>
-  <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>라스베가스(LAS)</t>
-  </si>
-  <si>
-    <t>15502</t>
-  </si>
-  <si>
-    <t>805</t>
-  </si>
-  <si>
-    <t>라이프치히(LEJ)</t>
-  </si>
-  <si>
-    <t>2234</t>
-  </si>
-  <si>
-    <t>랑군(RGN)</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>4609</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>런던히드로(LHR)</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>23237</t>
-  </si>
-  <si>
-    <t>2525</t>
-  </si>
-  <si>
-    <t>로마 파우미치노(FCO)</t>
-  </si>
-  <si>
-    <t>25359</t>
-  </si>
-  <si>
-    <t>1222</t>
-  </si>
-  <si>
-    <t>로스앤젤레스(LAX)</t>
-  </si>
-  <si>
-    <t>482</t>
-  </si>
-  <si>
-    <t>97941</t>
-  </si>
-  <si>
-    <t>14681</t>
-  </si>
-  <si>
-    <t>루이즈빌(SDF)</t>
-  </si>
-  <si>
-    <t>룩셈부르크(LUX)</t>
-  </si>
-  <si>
-    <t>1622</t>
-  </si>
-  <si>
-    <t>리마(LIM)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>리스본(LIS)</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>6197</t>
-  </si>
-  <si>
-    <t>288</t>
-  </si>
-  <si>
-    <t>리에쥬 비어셋(LGG)</t>
-  </si>
-  <si>
-    <t>마나스(FRU)</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>1576</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>마닐라(MNL)</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>149733</t>
-  </si>
-  <si>
-    <t>5523</t>
-  </si>
-  <si>
-    <t>마드리드(MAD)</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>7955</t>
-  </si>
-  <si>
-    <t>1677</t>
-  </si>
-  <si>
-    <t>마이애미(MIA)</t>
-  </si>
-  <si>
-    <t>903</t>
-  </si>
-  <si>
-    <t>마즈야마(MYJ)</t>
-  </si>
-  <si>
-    <t>21386</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>마카오(MFM)</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>34673</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>멕시코(MEX)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>8689</t>
-  </si>
-  <si>
-    <t>590</t>
-  </si>
-  <si>
-    <t>멜버른 툴라마린(MEL)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>597</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>멤피스(MEM)</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>몬테레이(MTY)</t>
-  </si>
-  <si>
-    <t>1977</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>무단지앙(MDG)</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1138</t>
-  </si>
-  <si>
-    <t>뮌헨(MUC)</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>13647</t>
-  </si>
-  <si>
-    <t>749</t>
-  </si>
-  <si>
-    <t>미네아폴리스(MSP)</t>
-  </si>
-  <si>
-    <t>17233</t>
-  </si>
-  <si>
-    <t>793</t>
-  </si>
-  <si>
-    <t>미와사키(KMI)</t>
-  </si>
-  <si>
-    <t>7685</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>밀라노(MXP)</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>9050</t>
-  </si>
-  <si>
-    <t>4548</t>
-  </si>
-  <si>
-    <t>바르샤바(WAW)</t>
-  </si>
-  <si>
-    <t>7870</t>
-  </si>
-  <si>
-    <t>508</t>
-  </si>
-  <si>
-    <t>바르셀로나(BCN)</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>20143</t>
-  </si>
-  <si>
-    <t>797</t>
-  </si>
-  <si>
-    <t>바탐(BTH)</t>
-  </si>
-  <si>
-    <t>1530</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>반다르세리베가완(BWN)</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>방콕(BKK)</t>
-  </si>
-  <si>
-    <t>825</t>
-  </si>
-  <si>
-    <t>205360</t>
-  </si>
-  <si>
-    <t>12238</t>
-  </si>
-  <si>
-    <t>뱅쿠버(YVR)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>43422</t>
-  </si>
-  <si>
-    <t>2280</t>
-  </si>
-  <si>
-    <t>보스톤(BOS)</t>
-  </si>
-  <si>
-    <t>14222</t>
-  </si>
-  <si>
-    <t>840</t>
-  </si>
-  <si>
-    <t>부다페스트(BUD)</t>
-  </si>
-  <si>
-    <t>8491</t>
-  </si>
-  <si>
-    <t>546</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>504</t>
-  </si>
-  <si>
-    <t>70312</t>
-  </si>
-  <si>
-    <t>1967</t>
-  </si>
-  <si>
-    <t>브라코프스(VCP)</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>브로츠와프(WRO)</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>프라하(PRG)</t>
+  </si>
+  <si>
+    <t>3311</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>프랑크푸르트(FRA)</t>
+  </si>
+  <si>
+    <t>20250</t>
+  </si>
+  <si>
+    <t>4223</t>
+  </si>
+  <si>
+    <t>프롬펜(PNH)</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>13098</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>필라델피아(PHL)</t>
+  </si>
+  <si>
+    <t>하노이(HAN)</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>60031</t>
+  </si>
+  <si>
+    <t>8019</t>
+  </si>
+  <si>
+    <t>하얼빈(HRB)</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>5303</t>
+  </si>
+  <si>
+    <t>하이커우(HAK)</t>
+  </si>
+  <si>
+    <t>1382</t>
+  </si>
+  <si>
+    <t>하이퐁(HPH)</t>
+  </si>
+  <si>
+    <t>4250</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>항조우(HGH)</t>
+  </si>
+  <si>
+    <t>15221</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>허폐(HFE)</t>
   </si>
   <si>
     <t>1695</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>브뤼셀(BRU)</t>
-  </si>
-  <si>
-    <t>926</t>
-  </si>
-  <si>
-    <t>브리스번(BNE)</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>14323</t>
-  </si>
-  <si>
-    <t>554</t>
-  </si>
-  <si>
-    <t>비엔나(VIE)</t>
-  </si>
-  <si>
-    <t>6811</t>
-  </si>
-  <si>
-    <t>2906</t>
-  </si>
-  <si>
-    <t>비엔티안(VTE)</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>34221</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>사가(HSG)</t>
-  </si>
-  <si>
-    <t>5721</t>
-  </si>
-  <si>
-    <t>사르고사(ZAZ)</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>사이판(SPN)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>21707</t>
-  </si>
-  <si>
-    <t>산야(SYX)</t>
-  </si>
-  <si>
-    <t>산티아고(SCL)</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>삿보로(치토세)(CTS)</t>
-  </si>
-  <si>
-    <t>556</t>
-  </si>
-  <si>
-    <t>93715</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>샌프란시스코(SFO)</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>68056</t>
-  </si>
-  <si>
-    <t>6408</t>
-  </si>
-  <si>
-    <t>샤먼(XMN)</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>18513</t>
-  </si>
-  <si>
-    <t>512</t>
-  </si>
-  <si>
-    <t>샤자르(SHJ)</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>세부(CEB)</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>59594</t>
-  </si>
-  <si>
-    <t>1273</t>
-  </si>
-  <si>
-    <t>센다이(SDJ)</t>
-  </si>
-  <si>
-    <t>6942</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>센젠(SZX)</t>
-  </si>
-  <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>45655</t>
-  </si>
-  <si>
-    <t>3156</t>
-  </si>
-  <si>
-    <t>쉬지아쭈앙(석가장)(SJW)</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>2987</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>스텐스테드(STN)</t>
-  </si>
-  <si>
-    <t>479</t>
-  </si>
-  <si>
-    <t>시드니(SYD)</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>61037</t>
-  </si>
-  <si>
-    <t>2431</t>
-  </si>
-  <si>
-    <t>시모지시마(SHI)</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>5033</t>
-  </si>
-  <si>
-    <t>시안(XIY)</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>15212</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>시애틀(SEA)</t>
-  </si>
-  <si>
-    <t>46706</t>
-  </si>
-  <si>
-    <t>3733</t>
-  </si>
-  <si>
-    <t>시즈오카(FSZ)</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>16724</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>시카고 록퍼드(RFD)</t>
-  </si>
-  <si>
-    <t>시카고(ORD)</t>
-  </si>
-  <si>
-    <t>14801</t>
-  </si>
-  <si>
-    <t>10307</t>
-  </si>
-  <si>
-    <t>신시내티(CVG)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>3569</t>
-  </si>
-  <si>
-    <t>심양(SHE)</t>
-  </si>
-  <si>
-    <t>34280</t>
-  </si>
-  <si>
-    <t>747</t>
-  </si>
-  <si>
-    <t>싱가폴(SIN)</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>163413</t>
-  </si>
-  <si>
-    <t>11659</t>
-  </si>
-  <si>
-    <t>씨엠립 앙코르(SAI)</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>아디스아바바(ADD)</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>4580</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>아사이까와(AKJ)</t>
-  </si>
-  <si>
-    <t>2991</t>
-  </si>
-  <si>
-    <t>아쉬가바트(ASB)</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>아오모리(AOJ)</t>
-  </si>
-  <si>
-    <t>3349</t>
-  </si>
-  <si>
-    <t>아틀란타(ATL)</t>
-  </si>
-  <si>
-    <t>52451</t>
-  </si>
-  <si>
-    <t>4695</t>
-  </si>
-  <si>
-    <t>알마아타(ALA)</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>12078</t>
-  </si>
-  <si>
-    <t>484</t>
-  </si>
-  <si>
-    <t>암스텔담(AMS)</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>20407</t>
-  </si>
-  <si>
-    <t>5096</t>
-  </si>
-  <si>
-    <t>앵커리지(ANC)</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>3763</t>
-  </si>
-  <si>
-    <t>양저우타이저우(YTY)</t>
-  </si>
-  <si>
-    <t>2665</t>
-  </si>
-  <si>
-    <t>어저우화후(EHU)</t>
-  </si>
-  <si>
-    <t>591</t>
-  </si>
-  <si>
-    <t>에드먼튼(YEG)</t>
-  </si>
-  <si>
-    <t>연길(YNJ)</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>37544</t>
-  </si>
-  <si>
-    <t>571</t>
-  </si>
-  <si>
-    <t>연대(YNT)</t>
-  </si>
-  <si>
-    <t>24847</t>
-  </si>
-  <si>
-    <t>3385</t>
-  </si>
-  <si>
-    <t>염성(YNZ)</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>2115</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>오까야마(OKJ)</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>4943</t>
-  </si>
-  <si>
-    <t>오끼나와(OKA)</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>74660</t>
-  </si>
-  <si>
-    <t>814</t>
-  </si>
-  <si>
-    <t>오스코다(OSC)</t>
-  </si>
-  <si>
-    <t>오슬로(OSL)</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>1728</t>
-  </si>
-  <si>
-    <t>오이다(OIT)</t>
-  </si>
-  <si>
-    <t>9296</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>오크랜드(미)(OAK)</t>
-  </si>
-  <si>
-    <t>오클랜드(AKL)</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>17837</t>
-  </si>
-  <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>온타리오(ONT)</t>
-  </si>
-  <si>
-    <t>요나고(YGJ)</t>
-  </si>
-  <si>
-    <t>4822</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>우시샤우팡(WUX)</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>11715</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>우한(무한)(WUH)</t>
-  </si>
-  <si>
-    <t>7144</t>
-  </si>
-  <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>우후(WHA)</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>481</t>
-  </si>
-  <si>
-    <t>울란바토르(신)(UBN)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>35556</t>
-  </si>
-  <si>
-    <t>1255</t>
-  </si>
-  <si>
-    <t>워싱턴 덜레스(IAD)</t>
-  </si>
-  <si>
-    <t>14164</t>
-  </si>
-  <si>
-    <t>956</t>
-  </si>
-  <si>
-    <t>원저우(WNZ)</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>웨이하이(WEH)</t>
-  </si>
-  <si>
-    <t>18265</t>
-  </si>
-  <si>
-    <t>1765</t>
-  </si>
-  <si>
-    <t>위니펙(YWG)</t>
-  </si>
-  <si>
-    <t>이스탄불(IST)</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>41193</t>
-  </si>
-  <si>
-    <t>4439</t>
-  </si>
-  <si>
-    <t>이스트미들랜드(EMA)</t>
-  </si>
-  <si>
-    <t>인디아나폴리스(IND)</t>
-  </si>
-  <si>
-    <t>자무쓰(JMU)</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>자이드(AUH)</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>17912</t>
-  </si>
-  <si>
-    <t>1553</t>
-  </si>
-  <si>
-    <t>자카르타(CGK)</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>31672</t>
-  </si>
-  <si>
-    <t>2514</t>
-  </si>
-  <si>
-    <t>장가계(대용)(DYG)</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>8683</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>장춘(CGQ)</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>11503</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>정저우(CGO)</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>10085</t>
-  </si>
-  <si>
-    <t>1817</t>
-  </si>
-  <si>
-    <t>지난(TNA)</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>15762</t>
-  </si>
-  <si>
-    <t>505</t>
-  </si>
-  <si>
-    <t>창사(CSX)</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>14686</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>천진(TSN)</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>21618</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>청도(TAO)</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>117015</t>
-  </si>
-  <si>
-    <t>3176</t>
-  </si>
-  <si>
-    <t>청두(CTU)</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>총킹(중경)(CKG)</t>
-  </si>
-  <si>
-    <t>5955</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>취리히(ZRH)</t>
-  </si>
-  <si>
-    <t>4098</t>
-  </si>
-  <si>
-    <t>792</t>
-  </si>
-  <si>
-    <t>치앙마이(CNX)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>46791</t>
-  </si>
-  <si>
-    <t>755</t>
-  </si>
-  <si>
-    <t>카고시마(KOJ)</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>13133</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>33169</t>
-  </si>
-  <si>
-    <t>카이로(CAI)</t>
-  </si>
-  <si>
-    <t>4116</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>카투만두(KTM)</t>
-  </si>
-  <si>
-    <t>4872</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>칼리보(KLO)</t>
-  </si>
-  <si>
-    <t>12989</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>코타키나발루(BKI)</t>
-  </si>
-  <si>
-    <t>42345</t>
-  </si>
-  <si>
-    <t>449</t>
-  </si>
-  <si>
-    <t>콜롬보(CMB)</t>
-  </si>
-  <si>
-    <t>쿠알라룸푸르(KUL)</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>51864</t>
-  </si>
-  <si>
-    <t>3390</t>
-  </si>
-  <si>
-    <t>쿤밍(KMG)</t>
-  </si>
-  <si>
-    <t>7682</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>퀼른(CGN)</t>
-  </si>
-  <si>
-    <t>클라크 필드(CRK)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>29351</t>
-  </si>
-  <si>
-    <t>437</t>
-  </si>
-  <si>
-    <t>키타큐슈(KKJ)</t>
-  </si>
-  <si>
-    <t>10648</t>
-  </si>
-  <si>
-    <t>757</t>
-  </si>
-  <si>
-    <t>타쉬켄트(TAS)</t>
-  </si>
-  <si>
-    <t>20504</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>타이페이(TPE)</t>
-  </si>
-  <si>
-    <t>741</t>
-  </si>
-  <si>
-    <t>213460</t>
-  </si>
-  <si>
-    <t>7758</t>
-  </si>
-  <si>
-    <t>타크빌라란(TAG)</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>41832</t>
-  </si>
-  <si>
-    <t>텐푸(TFU)</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>10978</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>토론토(YYZ)</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>30003</t>
-  </si>
-  <si>
-    <t>3015</t>
-  </si>
-  <si>
-    <t>파리 샤를드골(CDG)</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>49577</t>
-  </si>
-  <si>
-    <t>3890</t>
-  </si>
-  <si>
-    <t>페낭(PEN)</t>
-  </si>
-  <si>
-    <t>1848</t>
-  </si>
-  <si>
-    <t>푸동(PVG)</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>164068</t>
-  </si>
-  <si>
-    <t>19214</t>
-  </si>
-  <si>
-    <t>푸조우(FOC)</t>
-  </si>
-  <si>
-    <t>8945</t>
-  </si>
-  <si>
-    <t>푸켓(HKT)</t>
-  </si>
-  <si>
-    <t>20698</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>푸쿡(PQC)</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>80638</t>
-  </si>
-  <si>
-    <t>901</t>
-  </si>
-  <si>
-    <t>프라하(PRG)</t>
-  </si>
-  <si>
-    <t>6242</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>프랑크푸르트(FRA)</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>40707</t>
-  </si>
-  <si>
-    <t>8937</t>
-  </si>
-  <si>
-    <t>프롬펜(PNH)</t>
-  </si>
-  <si>
-    <t>28577</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>필라델피아(PHL)</t>
-  </si>
-  <si>
-    <t>하노이(HAN)</t>
-  </si>
-  <si>
-    <t>764</t>
-  </si>
-  <si>
-    <t>127871</t>
-  </si>
-  <si>
-    <t>15683</t>
-  </si>
-  <si>
-    <t>하얼빈(HRB)</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>13059</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>하이커우(HAK)</t>
-  </si>
-  <si>
-    <t>3899</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>하이퐁(HPH)</t>
-  </si>
-  <si>
-    <t>10740</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>항조우(HGH)</t>
-  </si>
-  <si>
-    <t>31815</t>
-  </si>
-  <si>
-    <t>503</t>
-  </si>
-  <si>
-    <t>허폐(HFE)</t>
-  </si>
-  <si>
-    <t>3594</t>
-  </si>
-  <si>
     <t>헤이다르 알리예프(GYD)</t>
   </si>
   <si>
-    <t>1776</t>
-  </si>
-  <si>
-    <t>헬리팍스(YHZ)</t>
-  </si>
-  <si>
-    <t>473</t>
+    <t>863</t>
   </si>
   <si>
     <t>헬싱키(HEL)</t>
   </si>
   <si>
-    <t>10027</t>
-  </si>
-  <si>
-    <t>1224</t>
+    <t>4723</t>
+  </si>
+  <si>
+    <t>528</t>
   </si>
   <si>
     <t>호놀룰루(HNL)</t>
   </si>
   <si>
-    <t>36032</t>
-  </si>
-  <si>
-    <t>1868</t>
+    <t>77</t>
+  </si>
+  <si>
+    <t>17058</t>
+  </si>
+  <si>
+    <t>1328</t>
   </si>
   <si>
     <t>호치민(SGN)</t>
   </si>
   <si>
-    <t>678</t>
-  </si>
-  <si>
-    <t>134558</t>
-  </si>
-  <si>
-    <t>6465</t>
+    <t>338</t>
+  </si>
+  <si>
+    <t>56354</t>
+  </si>
+  <si>
+    <t>2543</t>
   </si>
   <si>
     <t>홍콩(HKG)</t>
   </si>
   <si>
-    <t>1417</t>
-  </si>
-  <si>
-    <t>231005</t>
-  </si>
-  <si>
-    <t>23936</t>
+    <t>723</t>
+  </si>
+  <si>
+    <t>107977</t>
+  </si>
+  <si>
+    <t>8325</t>
   </si>
   <si>
     <t>후잔드(LBD)</t>
@@ -1871,22 +1712,19 @@
     <t>후쿠오카(FUK)</t>
   </si>
   <si>
-    <t>1426</t>
-  </si>
-  <si>
-    <t>311556</t>
-  </si>
-  <si>
-    <t>3967</t>
+    <t>713</t>
+  </si>
+  <si>
+    <t>156553</t>
+  </si>
+  <si>
+    <t>1855</t>
   </si>
   <si>
     <t>히로시마(HIJ)</t>
   </si>
   <si>
-    <t>15775</t>
-  </si>
-  <si>
-    <t>154</t>
+    <t>7719</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -2317,7 +2155,7 @@
         <v>75</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>15</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -2328,16 +2166,16 @@
         <v>11</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -2348,16 +2186,16 @@
         <v>11</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
@@ -2368,16 +2206,16 @@
         <v>11</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23">
@@ -2388,16 +2226,16 @@
         <v>11</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -2408,16 +2246,16 @@
         <v>11</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
@@ -2428,16 +2266,16 @@
         <v>11</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -2448,16 +2286,16 @@
         <v>11</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>103</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2611,7 +2449,7 @@
         <v>131</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>132</v>
@@ -2651,13 +2489,13 @@
         <v>138</v>
       </c>
       <c r="D36" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="E36" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="E36" t="s" s="0">
+      <c r="F36" t="s" s="0">
         <v>140</v>
-      </c>
-      <c r="F36" t="s" s="0">
-        <v>141</v>
       </c>
     </row>
     <row r="37">
@@ -2668,16 +2506,16 @@
         <v>11</v>
       </c>
       <c r="C37" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="D37" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="D37" t="s" s="0">
+      <c r="E37" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="E37" t="s" s="0">
+      <c r="F37" t="s" s="0">
         <v>144</v>
-      </c>
-      <c r="F37" t="s" s="0">
-        <v>145</v>
       </c>
     </row>
     <row r="38">
@@ -2688,16 +2526,16 @@
         <v>11</v>
       </c>
       <c r="C38" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="E38" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="D38" t="s" s="0">
-        <v>101</v>
-      </c>
-      <c r="E38" t="s" s="0">
+      <c r="F38" t="s" s="0">
         <v>147</v>
-      </c>
-      <c r="F38" t="s" s="0">
-        <v>148</v>
       </c>
     </row>
     <row r="39">
@@ -2708,16 +2546,16 @@
         <v>11</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>14</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>150</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -2728,16 +2566,16 @@
         <v>11</v>
       </c>
       <c r="C40" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F40" t="s" s="0">
         <v>151</v>
-      </c>
-      <c r="D40" t="s" s="0">
-        <v>152</v>
-      </c>
-      <c r="E40" t="s" s="0">
-        <v>153</v>
-      </c>
-      <c r="F40" t="s" s="0">
-        <v>154</v>
       </c>
     </row>
     <row r="41">
@@ -2748,16 +2586,16 @@
         <v>11</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42">
@@ -2768,16 +2606,16 @@
         <v>11</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s" s="0">
         <v>128</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43">
@@ -2788,16 +2626,16 @@
         <v>11</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F43" t="s" s="0">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44">
@@ -2808,10 +2646,10 @@
         <v>11</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>14</v>
@@ -2828,7 +2666,7 @@
         <v>11</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s" s="0">
         <v>21</v>
@@ -2837,7 +2675,7 @@
         <v>14</v>
       </c>
       <c r="F45" t="s" s="0">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46">
@@ -2848,16 +2686,16 @@
         <v>11</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>170</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47">
@@ -2868,16 +2706,16 @@
         <v>11</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48">
@@ -2888,16 +2726,16 @@
         <v>11</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>14</v>
+        <v>173</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>14</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49">
@@ -2908,16 +2746,16 @@
         <v>11</v>
       </c>
       <c r="C49" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="E49" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="D49" t="s" s="0">
+      <c r="F49" t="s" s="0">
         <v>177</v>
-      </c>
-      <c r="E49" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="F49" t="s" s="0">
-        <v>179</v>
       </c>
     </row>
     <row r="50">
@@ -2928,16 +2766,16 @@
         <v>11</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51">
@@ -2948,16 +2786,16 @@
         <v>11</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52">
@@ -2968,16 +2806,16 @@
         <v>11</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53">
@@ -2988,16 +2826,16 @@
         <v>11</v>
       </c>
       <c r="C53" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="F53" t="s" s="0">
         <v>190</v>
-      </c>
-      <c r="D53" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="E53" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="F53" t="s" s="0">
-        <v>192</v>
       </c>
     </row>
     <row r="54">
@@ -3008,16 +2846,16 @@
         <v>11</v>
       </c>
       <c r="C54" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="F54" t="s" s="0">
         <v>193</v>
-      </c>
-      <c r="D54" t="s" s="0">
-        <v>194</v>
-      </c>
-      <c r="E54" t="s" s="0">
-        <v>195</v>
-      </c>
-      <c r="F54" t="s" s="0">
-        <v>196</v>
       </c>
     </row>
     <row r="55">
@@ -3028,16 +2866,16 @@
         <v>11</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>199</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>200</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -3048,16 +2886,16 @@
         <v>11</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57">
@@ -3068,16 +2906,16 @@
         <v>11</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E57" t="s" s="0">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="F57" t="s" s="0">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58">
@@ -3088,16 +2926,16 @@
         <v>11</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59">
@@ -3108,16 +2946,16 @@
         <v>11</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60">
@@ -3128,16 +2966,16 @@
         <v>11</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s" s="0">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F60" t="s" s="0">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61">
@@ -3148,16 +2986,16 @@
         <v>11</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s" s="0">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F61" t="s" s="0">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62">
@@ -3168,16 +3006,16 @@
         <v>11</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="E62" t="s" s="0">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F62" t="s" s="0">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63">
@@ -3188,16 +3026,16 @@
         <v>11</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>227</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64">
@@ -3208,16 +3046,16 @@
         <v>11</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F64" t="s" s="0">
-        <v>230</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65">
@@ -3228,16 +3066,16 @@
         <v>11</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66">
@@ -3248,16 +3086,16 @@
         <v>11</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67">
@@ -3268,16 +3106,16 @@
         <v>11</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68">
@@ -3288,16 +3126,16 @@
         <v>11</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F68" t="s" s="0">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69">
@@ -3308,16 +3146,16 @@
         <v>11</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E69" t="s" s="0">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70">
@@ -3328,16 +3166,16 @@
         <v>11</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>250</v>
+        <v>14</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71">
@@ -3348,16 +3186,16 @@
         <v>11</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>254</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72">
@@ -3368,16 +3206,16 @@
         <v>11</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>257</v>
+        <v>14</v>
       </c>
       <c r="F72" t="s" s="0">
-        <v>258</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
@@ -3388,16 +3226,16 @@
         <v>11</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>177</v>
+        <v>98</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>14</v>
+        <v>250</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74">
@@ -3408,16 +3246,16 @@
         <v>11</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="E74" t="s" s="0">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75">
@@ -3428,16 +3266,16 @@
         <v>11</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>25</v>
+        <v>256</v>
       </c>
       <c r="E75" t="s" s="0">
-        <v>14</v>
+        <v>257</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76">
@@ -3448,16 +3286,16 @@
         <v>11</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>268</v>
+        <v>44</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="F76" t="s" s="0">
-        <v>270</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
@@ -3468,16 +3306,16 @@
         <v>11</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s" s="0">
-        <v>272</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>273</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
@@ -3488,16 +3326,16 @@
         <v>11</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>277</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79">
@@ -3508,16 +3346,16 @@
         <v>11</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="E79" t="s" s="0">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>23</v>
+        <v>267</v>
       </c>
     </row>
     <row r="80">
@@ -3528,16 +3366,16 @@
         <v>11</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>7</v>
+        <v>269</v>
       </c>
       <c r="E80" t="s" s="0">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="F80" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81">
@@ -3548,16 +3386,16 @@
         <v>11</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E81" t="s" s="0">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F81" t="s" s="0">
-        <v>174</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82">
@@ -3568,16 +3406,16 @@
         <v>11</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>117</v>
+        <v>277</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>25</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83">
@@ -3588,7 +3426,7 @@
         <v>11</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D83" t="s" s="0">
         <v>7</v>
@@ -3597,7 +3435,7 @@
         <v>14</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="84">
@@ -3608,16 +3446,16 @@
         <v>11</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F84" t="s" s="0">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85">
@@ -3628,16 +3466,16 @@
         <v>11</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>293</v>
+        <v>170</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86">
@@ -3648,16 +3486,16 @@
         <v>11</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87">
@@ -3668,16 +3506,16 @@
         <v>11</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>14</v>
+        <v>294</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>301</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
@@ -3688,16 +3526,16 @@
         <v>11</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>303</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="F88" t="s" s="0">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89">
@@ -3708,16 +3546,16 @@
         <v>11</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>23</v>
+        <v>298</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90">
@@ -3728,16 +3566,16 @@
         <v>11</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>310</v>
+        <v>23</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="F90" t="s" s="0">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="91">
@@ -3748,16 +3586,16 @@
         <v>11</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="92">
@@ -3768,16 +3606,16 @@
         <v>11</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>7</v>
+        <v>308</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="F92" t="s" s="0">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="93">
@@ -3788,16 +3626,16 @@
         <v>11</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="94">
@@ -3808,16 +3646,16 @@
         <v>11</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>324</v>
+        <v>126</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>325</v>
+        <v>14</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>215</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -3828,16 +3666,16 @@
         <v>11</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>329</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96">
@@ -3848,16 +3686,16 @@
         <v>11</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>331</v>
+        <v>14</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>332</v>
+        <v>321</v>
       </c>
     </row>
     <row r="97">
@@ -3868,16 +3706,16 @@
         <v>11</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="F97" t="s" s="0">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="98">
@@ -3888,16 +3726,16 @@
         <v>11</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>14</v>
+        <v>327</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="99">
@@ -3908,16 +3746,16 @@
         <v>11</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>339</v>
+        <v>14</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>340</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100">
@@ -3928,16 +3766,16 @@
         <v>11</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>342</v>
+        <v>65</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>14</v>
+        <v>331</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>343</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101">
@@ -3948,16 +3786,16 @@
         <v>11</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="F101" t="s" s="0">
-        <v>346</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102">
@@ -3968,16 +3806,16 @@
         <v>11</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>348</v>
+        <v>197</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>349</v>
+        <v>14</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>350</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103">
@@ -3988,16 +3826,16 @@
         <v>11</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>352</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s" s="0">
-        <v>133</v>
+        <v>337</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>353</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104">
@@ -4008,16 +3846,16 @@
         <v>11</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
     <row r="105">
@@ -4028,16 +3866,16 @@
         <v>11</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>44</v>
+        <v>343</v>
       </c>
       <c r="E105" t="s" s="0">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="F105" t="s" s="0">
-        <v>44</v>
+        <v>345</v>
       </c>
     </row>
     <row r="106">
@@ -4048,16 +3886,16 @@
         <v>11</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="E106" t="s" s="0">
-        <v>14</v>
+        <v>347</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="107">
@@ -4068,16 +3906,16 @@
         <v>11</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E107" t="s" s="0">
-        <v>363</v>
+        <v>14</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="108">
@@ -4088,16 +3926,16 @@
         <v>11</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>342</v>
+        <v>168</v>
       </c>
       <c r="E108" t="s" s="0">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>366</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
@@ -4108,16 +3946,16 @@
         <v>11</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>368</v>
+        <v>67</v>
       </c>
       <c r="E109" t="s" s="0">
-        <v>369</v>
+        <v>14</v>
       </c>
       <c r="F109" t="s" s="0">
-        <v>370</v>
+        <v>354</v>
       </c>
     </row>
     <row r="110">
@@ -4128,16 +3966,16 @@
         <v>11</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="E110" t="s" s="0">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>374</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111">
@@ -4148,16 +3986,16 @@
         <v>11</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="E111" t="s" s="0">
-        <v>14</v>
+        <v>361</v>
       </c>
       <c r="F111" t="s" s="0">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112">
@@ -4168,16 +4006,16 @@
         <v>11</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>177</v>
+        <v>303</v>
       </c>
       <c r="E112" t="s" s="0">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="F112" t="s" s="0">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113">
@@ -4188,16 +4026,16 @@
         <v>11</v>
       </c>
       <c r="C113" t="s" s="0">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>15</v>
+        <v>366</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>14</v>
+        <v>367</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>381</v>
+        <v>188</v>
       </c>
     </row>
     <row r="114">
@@ -4208,16 +4046,16 @@
         <v>11</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>7</v>
+        <v>369</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>14</v>
+        <v>370</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>14</v>
+        <v>371</v>
       </c>
     </row>
     <row r="115">
@@ -4228,16 +4066,16 @@
         <v>11</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>384</v>
+        <v>193</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>385</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>386</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116">
@@ -4248,16 +4086,16 @@
         <v>11</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="E116" t="s" s="0">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="F116" t="s" s="0">
-        <v>389</v>
+        <v>375</v>
       </c>
     </row>
     <row r="117">
@@ -4268,16 +4106,16 @@
         <v>11</v>
       </c>
       <c r="C117" t="s" s="0">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>391</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>392</v>
+        <v>14</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>393</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
@@ -4288,16 +4126,16 @@
         <v>11</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>395</v>
+        <v>343</v>
       </c>
       <c r="E118" t="s" s="0">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="F118" t="s" s="0">
-        <v>97</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119">
@@ -4308,16 +4146,16 @@
         <v>11</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120">
@@ -4328,16 +4166,16 @@
         <v>11</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>7</v>
+        <v>384</v>
       </c>
       <c r="E120" t="s" s="0">
-        <v>14</v>
+        <v>385</v>
       </c>
       <c r="F120" t="s" s="0">
-        <v>14</v>
+        <v>358</v>
       </c>
     </row>
     <row r="121">
@@ -4348,16 +4186,16 @@
         <v>11</v>
       </c>
       <c r="C121" t="s" s="0">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>14</v>
+        <v>387</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>404</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122">
@@ -4368,16 +4206,16 @@
         <v>11</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>268</v>
+        <v>201</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>406</v>
+        <v>14</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>407</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123">
@@ -4388,16 +4226,16 @@
         <v>11</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>14</v>
+        <v>391</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>14</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124">
@@ -4408,16 +4246,16 @@
         <v>11</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>410</v>
+        <v>102</v>
       </c>
       <c r="E124" t="s" s="0">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="F124" t="s" s="0">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125">
@@ -4428,16 +4266,16 @@
         <v>11</v>
       </c>
       <c r="C125" t="s" s="0">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>7</v>
+        <v>218</v>
       </c>
       <c r="E125" t="s" s="0">
-        <v>14</v>
+        <v>397</v>
       </c>
       <c r="F125" t="s" s="0">
-        <v>14</v>
+        <v>398</v>
       </c>
     </row>
     <row r="126">
@@ -4448,16 +4286,16 @@
         <v>11</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="E126" t="s" s="0">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="F126" t="s" s="0">
-        <v>416</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127">
@@ -4468,16 +4306,16 @@
         <v>11</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>418</v>
+        <v>151</v>
       </c>
       <c r="E127" t="s" s="0">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="F127" t="s" s="0">
-        <v>420</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128">
@@ -4488,16 +4326,16 @@
         <v>11</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>395</v>
+        <v>13</v>
       </c>
       <c r="E128" t="s" s="0">
-        <v>422</v>
+        <v>14</v>
       </c>
       <c r="F128" t="s" s="0">
-        <v>423</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129">
@@ -4508,16 +4346,16 @@
         <v>11</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>425</v>
+        <v>312</v>
       </c>
       <c r="E129" t="s" s="0">
         <v>14</v>
       </c>
       <c r="F129" t="s" s="0">
-        <v>426</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130">
@@ -4528,16 +4366,16 @@
         <v>11</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>428</v>
+        <v>246</v>
       </c>
       <c r="E130" t="s" s="0">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>430</v>
+        <v>61</v>
       </c>
     </row>
     <row r="131">
@@ -4548,16 +4386,16 @@
         <v>11</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>101</v>
+        <v>409</v>
       </c>
       <c r="E131" t="s" s="0">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="F131" t="s" s="0">
-        <v>433</v>
+        <v>411</v>
       </c>
     </row>
     <row r="132">
@@ -4568,16 +4406,16 @@
         <v>11</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>368</v>
+        <v>263</v>
       </c>
       <c r="E132" t="s" s="0">
-        <v>50</v>
+        <v>413</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>435</v>
+        <v>414</v>
       </c>
     </row>
     <row r="133">
@@ -4588,16 +4426,16 @@
         <v>11</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="E133" t="s" s="0">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="F133" t="s" s="0">
-        <v>438</v>
+        <v>409</v>
       </c>
     </row>
     <row r="134">
@@ -4608,16 +4446,16 @@
         <v>11</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>7</v>
+        <v>375</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>14</v>
+        <v>418</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>14</v>
+        <v>419</v>
       </c>
     </row>
     <row r="135">
@@ -4628,16 +4466,16 @@
         <v>11</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="D135" t="s" s="0">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="E135" t="s" s="0">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="F135" t="s" s="0">
-        <v>443</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136">
@@ -4648,16 +4486,16 @@
         <v>11</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>202</v>
+        <v>424</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>14</v>
+        <v>425</v>
       </c>
       <c r="F136" t="s" s="0">
-        <v>14</v>
+        <v>426</v>
       </c>
     </row>
     <row r="137">
@@ -4668,16 +4506,16 @@
         <v>11</v>
       </c>
       <c r="C137" t="s" s="0">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="D137" t="s" s="0">
-        <v>185</v>
+        <v>428</v>
       </c>
       <c r="E137" t="s" s="0">
-        <v>14</v>
+        <v>429</v>
       </c>
       <c r="F137" t="s" s="0">
-        <v>334</v>
+        <v>314</v>
       </c>
     </row>
     <row r="138">
@@ -4688,16 +4526,16 @@
         <v>11</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>353</v>
+        <v>71</v>
       </c>
       <c r="E138" t="s" s="0">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="F138" t="s" s="0">
-        <v>177</v>
+        <v>432</v>
       </c>
     </row>
     <row r="139">
@@ -4708,16 +4546,16 @@
         <v>11</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="E139" t="s" s="0">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="F139" t="s" s="0">
-        <v>451</v>
+        <v>436</v>
       </c>
     </row>
     <row r="140">
@@ -4728,16 +4566,16 @@
         <v>11</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>453</v>
+        <v>63</v>
       </c>
       <c r="E140" t="s" s="0">
-        <v>454</v>
+        <v>14</v>
       </c>
       <c r="F140" t="s" s="0">
-        <v>455</v>
+        <v>109</v>
       </c>
     </row>
     <row r="141">
@@ -4748,16 +4586,16 @@
         <v>11</v>
       </c>
       <c r="C141" t="s" s="0">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="D141" t="s" s="0">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E141" t="s" s="0">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F141" t="s" s="0">
-        <v>459</v>
+        <v>441</v>
       </c>
     </row>
     <row r="142">
@@ -4768,16 +4606,16 @@
         <v>11</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>461</v>
+        <v>126</v>
       </c>
       <c r="E142" t="s" s="0">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="F142" t="s" s="0">
-        <v>463</v>
+        <v>444</v>
       </c>
     </row>
     <row r="143">
@@ -4788,16 +4626,16 @@
         <v>11</v>
       </c>
       <c r="C143" t="s" s="0">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="D143" t="s" s="0">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="E143" t="s" s="0">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="F143" t="s" s="0">
-        <v>467</v>
+        <v>448</v>
       </c>
     </row>
     <row r="144">
@@ -4808,16 +4646,16 @@
         <v>11</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>469</v>
+        <v>92</v>
       </c>
       <c r="E144" t="s" s="0">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="F144" t="s" s="0">
-        <v>471</v>
+        <v>451</v>
       </c>
     </row>
     <row r="145">
@@ -4828,16 +4666,16 @@
         <v>11</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="F145" t="s" s="0">
-        <v>475</v>
+        <v>455</v>
       </c>
     </row>
     <row r="146">
@@ -4848,16 +4686,16 @@
         <v>11</v>
       </c>
       <c r="C146" t="s" s="0">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="D146" t="s" s="0">
-        <v>477</v>
+        <v>193</v>
       </c>
       <c r="E146" t="s" s="0">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="F146" t="s" s="0">
-        <v>479</v>
+        <v>211</v>
       </c>
     </row>
     <row r="147">
@@ -4868,16 +4706,16 @@
         <v>11</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>481</v>
+        <v>293</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="F147" t="s" s="0">
-        <v>483</v>
+        <v>282</v>
       </c>
     </row>
     <row r="148">
@@ -4888,16 +4726,16 @@
         <v>11</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>14</v>
+        <v>462</v>
       </c>
       <c r="F148" t="s" s="0">
-        <v>486</v>
+        <v>463</v>
       </c>
     </row>
     <row r="149">
@@ -4908,16 +4746,16 @@
         <v>11</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>46</v>
+        <v>465</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="F149" t="s" s="0">
-        <v>489</v>
+        <v>467</v>
       </c>
     </row>
     <row r="150">
@@ -4928,16 +4766,16 @@
         <v>11</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="D150" t="s" s="0">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="F150" t="s" s="0">
-        <v>492</v>
+        <v>470</v>
       </c>
     </row>
     <row r="151">
@@ -4948,16 +4786,16 @@
         <v>11</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="F151" t="s" s="0">
-        <v>496</v>
+        <v>474</v>
       </c>
     </row>
     <row r="152">
@@ -4968,16 +4806,16 @@
         <v>11</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>498</v>
+        <v>102</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="F152" t="s" s="0">
-        <v>154</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153">
@@ -4988,16 +4826,16 @@
         <v>11</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>501</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>502</v>
+        <v>14</v>
       </c>
       <c r="F153" t="s" s="0">
-        <v>256</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154">
@@ -5008,16 +4846,16 @@
         <v>11</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>204</v>
+        <v>388</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="F154" t="s" s="0">
-        <v>505</v>
+        <v>480</v>
       </c>
     </row>
     <row r="155">
@@ -5028,16 +4866,16 @@
         <v>11</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>314</v>
+        <v>439</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="F155" t="s" s="0">
-        <v>508</v>
+        <v>483</v>
       </c>
     </row>
     <row r="156">
@@ -5048,16 +4886,16 @@
         <v>11</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>103</v>
+        <v>312</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="F156" t="s" s="0">
-        <v>511</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157">
@@ -5068,16 +4906,16 @@
         <v>11</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>310</v>
+        <v>172</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="F157" t="s" s="0">
-        <v>514</v>
+        <v>489</v>
       </c>
     </row>
     <row r="158">
@@ -5088,16 +4926,16 @@
         <v>11</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>177</v>
+        <v>491</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>363</v>
+        <v>492</v>
       </c>
       <c r="F158" t="s" s="0">
-        <v>207</v>
+        <v>493</v>
       </c>
     </row>
     <row r="159">
@@ -5108,16 +4946,16 @@
         <v>11</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>517</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="F159" t="s" s="0">
-        <v>519</v>
+        <v>496</v>
       </c>
     </row>
     <row r="160">
@@ -5128,16 +4966,16 @@
         <v>11</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="F160" t="s" s="0">
-        <v>522</v>
+        <v>499</v>
       </c>
     </row>
     <row r="161">
@@ -5148,16 +4986,16 @@
         <v>11</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>14</v>
+        <v>501</v>
       </c>
       <c r="F161" t="s" s="0">
-        <v>14</v>
+        <v>502</v>
       </c>
     </row>
     <row r="162">
@@ -5168,16 +5006,16 @@
         <v>11</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="E162" t="s" s="0">
-        <v>526</v>
+        <v>14</v>
       </c>
       <c r="F162" t="s" s="0">
-        <v>527</v>
+        <v>504</v>
       </c>
     </row>
     <row r="163">
@@ -5188,16 +5026,16 @@
         <v>11</v>
       </c>
       <c r="C163" t="s" s="0">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="D163" t="s" s="0">
-        <v>46</v>
+        <v>506</v>
       </c>
       <c r="E163" t="s" s="0">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="F163" t="s" s="0">
-        <v>530</v>
+        <v>508</v>
       </c>
     </row>
     <row r="164">
@@ -5208,16 +5046,16 @@
         <v>11</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>334</v>
+        <v>287</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="F164" t="s" s="0">
-        <v>533</v>
+        <v>78</v>
       </c>
     </row>
     <row r="165">
@@ -5228,16 +5066,16 @@
         <v>11</v>
       </c>
       <c r="C165" t="s" s="0">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="D165" t="s" s="0">
-        <v>535</v>
+        <v>195</v>
       </c>
       <c r="E165" t="s" s="0">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="F165" t="s" s="0">
-        <v>537</v>
+        <v>513</v>
       </c>
     </row>
     <row r="166">
@@ -5248,16 +5086,16 @@
         <v>11</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F166" t="s" s="0">
-        <v>527</v>
+        <v>517</v>
       </c>
     </row>
     <row r="167">
@@ -5268,16 +5106,16 @@
         <v>11</v>
       </c>
       <c r="C167" t="s" s="0">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="D167" t="s" s="0">
-        <v>542</v>
+        <v>25</v>
       </c>
       <c r="E167" t="s" s="0">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="F167" t="s" s="0">
-        <v>544</v>
+        <v>520</v>
       </c>
     </row>
     <row r="168">
@@ -5288,16 +5126,16 @@
         <v>11</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>546</v>
+        <v>354</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="F168" t="s" s="0">
-        <v>548</v>
+        <v>523</v>
       </c>
     </row>
     <row r="169">
@@ -5308,16 +5146,16 @@
         <v>11</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="F169" t="s" s="0">
-        <v>552</v>
+        <v>527</v>
       </c>
     </row>
     <row r="170">
@@ -5328,16 +5166,16 @@
         <v>11</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E170" t="s" s="0">
         <v>14</v>
       </c>
       <c r="F170" t="s" s="0">
-        <v>554</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171">
@@ -5348,16 +5186,16 @@
         <v>11</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="D171" t="s" s="0">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="E171" t="s" s="0">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="F171" t="s" s="0">
-        <v>558</v>
+        <v>532</v>
       </c>
     </row>
     <row r="172">
@@ -5368,16 +5206,16 @@
         <v>11</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>264</v>
+        <v>534</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="F172" t="s" s="0">
-        <v>287</v>
+        <v>496</v>
       </c>
     </row>
     <row r="173">
@@ -5388,16 +5226,16 @@
         <v>11</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>561</v>
+        <v>536</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>407</v>
+        <v>44</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>562</v>
+        <v>537</v>
       </c>
       <c r="F173" t="s" s="0">
-        <v>563</v>
+        <v>100</v>
       </c>
     </row>
     <row r="174">
@@ -5408,16 +5246,16 @@
         <v>11</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>565</v>
+        <v>102</v>
       </c>
       <c r="E174" t="s" s="0">
-        <v>566</v>
+        <v>539</v>
       </c>
       <c r="F174" t="s" s="0">
-        <v>567</v>
+        <v>540</v>
       </c>
     </row>
     <row r="175">
@@ -5428,16 +5266,16 @@
         <v>11</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>568</v>
+        <v>541</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="E175" t="s" s="0">
-        <v>569</v>
+        <v>542</v>
       </c>
       <c r="F175" t="s" s="0">
-        <v>570</v>
+        <v>543</v>
       </c>
     </row>
     <row r="176">
@@ -5448,16 +5286,16 @@
         <v>11</v>
       </c>
       <c r="C176" t="s" s="0">
-        <v>571</v>
+        <v>544</v>
       </c>
       <c r="D176" t="s" s="0">
-        <v>572</v>
+        <v>21</v>
       </c>
       <c r="E176" t="s" s="0">
-        <v>573</v>
+        <v>545</v>
       </c>
       <c r="F176" t="s" s="0">
-        <v>574</v>
+        <v>382</v>
       </c>
     </row>
     <row r="177">
@@ -5468,16 +5306,16 @@
         <v>11</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>575</v>
+        <v>546</v>
       </c>
       <c r="D177" t="s" s="0">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>576</v>
+        <v>14</v>
       </c>
       <c r="F177" t="s" s="0">
-        <v>577</v>
+        <v>547</v>
       </c>
     </row>
     <row r="178">
@@ -5488,16 +5326,16 @@
         <v>11</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>578</v>
+        <v>548</v>
       </c>
       <c r="D178" t="s" s="0">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>14</v>
+        <v>549</v>
       </c>
       <c r="F178" t="s" s="0">
-        <v>14</v>
+        <v>550</v>
       </c>
     </row>
     <row r="179">
@@ -5508,16 +5346,16 @@
         <v>11</v>
       </c>
       <c r="C179" t="s" s="0">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="D179" t="s" s="0">
-        <v>580</v>
+        <v>552</v>
       </c>
       <c r="E179" t="s" s="0">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="F179" t="s" s="0">
-        <v>582</v>
+        <v>554</v>
       </c>
     </row>
     <row r="180">
@@ -5528,16 +5366,16 @@
         <v>11</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="D180" t="s" s="0">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="F180" t="s" s="0">
-        <v>586</v>
+        <v>558</v>
       </c>
     </row>
     <row r="181">
@@ -5548,16 +5386,16 @@
         <v>11</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>587</v>
+        <v>559</v>
       </c>
       <c r="D181" t="s" s="0">
-        <v>44</v>
+        <v>560</v>
       </c>
       <c r="E181" t="s" s="0">
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="F181" t="s" s="0">
-        <v>589</v>
+        <v>562</v>
       </c>
     </row>
     <row r="182">
@@ -5568,16 +5406,16 @@
         <v>11</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="D182" t="s" s="0">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>591</v>
+        <v>14</v>
       </c>
       <c r="F182" t="s" s="0">
-        <v>592</v>
+        <v>564</v>
       </c>
     </row>
     <row r="183">
@@ -5588,16 +5426,16 @@
         <v>11</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>593</v>
+        <v>565</v>
       </c>
       <c r="D183" t="s" s="0">
-        <v>56</v>
+        <v>566</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="F183" t="s" s="0">
-        <v>595</v>
+        <v>568</v>
       </c>
     </row>
     <row r="184">
@@ -5608,196 +5446,16 @@
         <v>11</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>596</v>
+        <v>569</v>
       </c>
       <c r="D184" t="s" s="0">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E184" t="s" s="0">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="F184" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n" s="0">
-        <v>183.0</v>
-      </c>
-      <c r="B185" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C185" t="s" s="0">
-        <v>598</v>
-      </c>
-      <c r="D185" t="s" s="0">
-        <v>314</v>
-      </c>
-      <c r="E185" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="F185" t="s" s="0">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n" s="0">
-        <v>184.0</v>
-      </c>
-      <c r="B186" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C186" t="s" s="0">
-        <v>600</v>
-      </c>
-      <c r="D186" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E186" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="F186" t="s" s="0">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n" s="0">
-        <v>185.0</v>
-      </c>
-      <c r="B187" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C187" t="s" s="0">
-        <v>602</v>
-      </c>
-      <c r="D187" t="s" s="0">
-        <v>425</v>
-      </c>
-      <c r="E187" t="s" s="0">
-        <v>603</v>
-      </c>
-      <c r="F187" t="s" s="0">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n" s="0">
-        <v>186.0</v>
-      </c>
-      <c r="B188" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C188" t="s" s="0">
-        <v>605</v>
-      </c>
-      <c r="D188" t="s" s="0">
-        <v>287</v>
-      </c>
-      <c r="E188" t="s" s="0">
-        <v>606</v>
-      </c>
-      <c r="F188" t="s" s="0">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n" s="0">
-        <v>187.0</v>
-      </c>
-      <c r="B189" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C189" t="s" s="0">
-        <v>608</v>
-      </c>
-      <c r="D189" t="s" s="0">
-        <v>609</v>
-      </c>
-      <c r="E189" t="s" s="0">
-        <v>610</v>
-      </c>
-      <c r="F189" t="s" s="0">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="B190" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C190" t="s" s="0">
-        <v>612</v>
-      </c>
-      <c r="D190" t="s" s="0">
-        <v>613</v>
-      </c>
-      <c r="E190" t="s" s="0">
-        <v>614</v>
-      </c>
-      <c r="F190" t="s" s="0">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n" s="0">
-        <v>189.0</v>
-      </c>
-      <c r="B191" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C191" t="s" s="0">
-        <v>616</v>
-      </c>
-      <c r="D191" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="E191" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="F191" t="s" s="0">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n" s="0">
-        <v>190.0</v>
-      </c>
-      <c r="B192" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C192" t="s" s="0">
-        <v>618</v>
-      </c>
-      <c r="D192" t="s" s="0">
-        <v>619</v>
-      </c>
-      <c r="E192" t="s" s="0">
-        <v>620</v>
-      </c>
-      <c r="F192" t="s" s="0">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n" s="0">
-        <v>191.0</v>
-      </c>
-      <c r="B193" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C193" t="s" s="0">
-        <v>622</v>
-      </c>
-      <c r="D193" t="s" s="0">
-        <v>473</v>
-      </c>
-      <c r="E193" t="s" s="0">
-        <v>623</v>
-      </c>
-      <c r="F193" t="s" s="0">
-        <v>624</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
